--- a/output/yearly_population_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_64_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5426</v>
+        <v>4091</v>
       </c>
       <c r="C2" t="n">
-        <v>6731</v>
+        <v>6359</v>
       </c>
       <c r="D2" t="n">
-        <v>31099</v>
+        <v>26941</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3748</v>
+        <v>2709</v>
       </c>
       <c r="C3" t="n">
-        <v>5045</v>
+        <v>2949</v>
       </c>
       <c r="D3" t="n">
-        <v>15957</v>
+        <v>18649</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>2077</v>
       </c>
       <c r="C4" t="n">
-        <v>5130</v>
+        <v>3351</v>
       </c>
       <c r="D4" t="n">
-        <v>7797</v>
+        <v>10329</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1833</v>
+        <v>1420</v>
       </c>
       <c r="C5" t="n">
-        <v>4506</v>
+        <v>3222</v>
       </c>
       <c r="D5" t="n">
-        <v>3261</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1047</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>2987</v>
+        <v>2564</v>
       </c>
       <c r="D6" t="n">
-        <v>1340</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>684</v>
+        <v>786</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -940,7 +940,7 @@
         <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6042</v>
+        <v>5908</v>
       </c>
       <c r="C2" t="n">
-        <v>5185</v>
+        <v>7791</v>
       </c>
       <c r="D2" t="n">
-        <v>29155</v>
+        <v>36447</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3707</v>
+        <v>2713</v>
       </c>
       <c r="C3" t="n">
-        <v>5114</v>
+        <v>3981</v>
       </c>
       <c r="D3" t="n">
-        <v>16944</v>
+        <v>18523</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2747</v>
+        <v>2013</v>
       </c>
       <c r="C4" t="n">
-        <v>4982</v>
+        <v>3084</v>
       </c>
       <c r="D4" t="n">
-        <v>8891</v>
+        <v>11273</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1991</v>
+        <v>1512</v>
       </c>
       <c r="C5" t="n">
-        <v>4656</v>
+        <v>3184</v>
       </c>
       <c r="D5" t="n">
-        <v>3827</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1260</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>3643</v>
+        <v>2841</v>
       </c>
       <c r="D6" t="n">
-        <v>1617</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>669</v>
+        <v>556</v>
       </c>
       <c r="C7" t="n">
-        <v>2212</v>
+        <v>2040</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>1092</v>
+        <v>1163</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>456</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
+        <v>267</v>
+      </c>
+      <c r="D10" t="n">
         <v>245</v>
-      </c>
-      <c r="D10" t="n">
-        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7067</v>
+        <v>8244</v>
       </c>
       <c r="C2" t="n">
-        <v>7227</v>
+        <v>14339</v>
       </c>
       <c r="D2" t="n">
-        <v>26413</v>
+        <v>40575</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3794</v>
+        <v>3253</v>
       </c>
       <c r="C3" t="n">
-        <v>4559</v>
+        <v>4954</v>
       </c>
       <c r="D3" t="n">
-        <v>17395</v>
+        <v>19602</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2674</v>
+        <v>1964</v>
       </c>
       <c r="C4" t="n">
-        <v>4936</v>
+        <v>3424</v>
       </c>
       <c r="D4" t="n">
-        <v>9857</v>
+        <v>12043</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2043</v>
+        <v>1545</v>
       </c>
       <c r="C5" t="n">
-        <v>4652</v>
+        <v>3044</v>
       </c>
       <c r="D5" t="n">
-        <v>4403</v>
+        <v>5654</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1430</v>
+        <v>1120</v>
       </c>
       <c r="C6" t="n">
-        <v>3992</v>
+        <v>2959</v>
       </c>
       <c r="D6" t="n">
-        <v>1913</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>810</v>
+        <v>671</v>
       </c>
       <c r="C7" t="n">
-        <v>2800</v>
+        <v>2348</v>
       </c>
       <c r="D7" t="n">
-        <v>871</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>384</v>
+        <v>323</v>
       </c>
       <c r="C8" t="n">
-        <v>1519</v>
+        <v>1503</v>
       </c>
       <c r="D8" t="n">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C9" t="n">
-        <v>698</v>
+        <v>776</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6470</v>
+        <v>7267</v>
       </c>
       <c r="C2" t="n">
-        <v>4914</v>
+        <v>9635</v>
       </c>
       <c r="D2" t="n">
-        <v>21798</v>
+        <v>33212</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4702</v>
+        <v>3779</v>
       </c>
       <c r="C3" t="n">
-        <v>7234</v>
+        <v>7938</v>
       </c>
       <c r="D3" t="n">
-        <v>19059</v>
+        <v>21649</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1887</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>7214</v>
+        <v>4861</v>
       </c>
       <c r="D4" t="n">
-        <v>9478</v>
+        <v>11831</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1321</v>
+        <v>1034</v>
       </c>
       <c r="C5" t="n">
-        <v>3912</v>
+        <v>2899</v>
       </c>
       <c r="D5" t="n">
-        <v>3058</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>748</v>
+        <v>620</v>
       </c>
       <c r="C6" t="n">
-        <v>2744</v>
+        <v>2301</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>1488</v>
+        <v>1472</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>684</v>
+        <v>760</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4072</v>
+        <v>4140</v>
       </c>
       <c r="C2" t="n">
-        <v>2368</v>
+        <v>3993</v>
       </c>
       <c r="D2" t="n">
-        <v>14911</v>
+        <v>23347</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4726</v>
+        <v>4476</v>
       </c>
       <c r="C3" t="n">
-        <v>5585</v>
+        <v>7894</v>
       </c>
       <c r="D3" t="n">
-        <v>18333</v>
+        <v>21974</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2607</v>
+        <v>2038</v>
       </c>
       <c r="C4" t="n">
-        <v>7350</v>
+        <v>6393</v>
       </c>
       <c r="D4" t="n">
-        <v>10843</v>
+        <v>13206</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1451</v>
+        <v>1125</v>
       </c>
       <c r="C5" t="n">
-        <v>5381</v>
+        <v>3759</v>
       </c>
       <c r="D5" t="n">
-        <v>3824</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>736</v>
       </c>
       <c r="C6" t="n">
-        <v>3288</v>
+        <v>2653</v>
       </c>
       <c r="D6" t="n">
-        <v>1079</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>1963</v>
+        <v>1828</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>912</v>
+        <v>984</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4460</v>
+        <v>3285</v>
       </c>
       <c r="C2" t="n">
-        <v>4131</v>
+        <v>6600</v>
       </c>
       <c r="D2" t="n">
-        <v>20417</v>
+        <v>25991</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3736</v>
+        <v>3636</v>
       </c>
       <c r="C3" t="n">
-        <v>3558</v>
+        <v>5330</v>
       </c>
       <c r="D3" t="n">
-        <v>16754</v>
+        <v>20870</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3046</v>
+        <v>2660</v>
       </c>
       <c r="C4" t="n">
-        <v>6316</v>
+        <v>7009</v>
       </c>
       <c r="D4" t="n">
-        <v>11631</v>
+        <v>14108</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1724</v>
+        <v>1342</v>
       </c>
       <c r="C5" t="n">
-        <v>6265</v>
+        <v>4981</v>
       </c>
       <c r="D5" t="n">
-        <v>4853</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>829</v>
       </c>
       <c r="C6" t="n">
-        <v>4200</v>
+        <v>3126</v>
       </c>
       <c r="D6" t="n">
-        <v>1486</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>2565</v>
+        <v>2209</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>1353</v>
+        <v>1340</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>580</v>
+        <v>631</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="D10" t="n">
         <v>215</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2620</v>
+        <v>1927</v>
       </c>
       <c r="C2" t="n">
-        <v>1932</v>
+        <v>3028</v>
       </c>
       <c r="D2" t="n">
-        <v>14087</v>
+        <v>17994</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3807</v>
+        <v>3452</v>
       </c>
       <c r="C3" t="n">
-        <v>3641</v>
+        <v>5596</v>
       </c>
       <c r="D3" t="n">
-        <v>16762</v>
+        <v>20942</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3359</v>
+        <v>2948</v>
       </c>
       <c r="C4" t="n">
-        <v>5864</v>
+        <v>6971</v>
       </c>
       <c r="D4" t="n">
-        <v>12374</v>
+        <v>15062</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1801</v>
+        <v>1413</v>
       </c>
       <c r="C5" t="n">
-        <v>7253</v>
+        <v>6195</v>
       </c>
       <c r="D5" t="n">
-        <v>5219</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>5075</v>
+        <v>3889</v>
       </c>
       <c r="D6" t="n">
-        <v>1441</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2610</v>
+        <v>2365</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>1038</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2920</v>
+        <v>2587</v>
       </c>
       <c r="C2" t="n">
-        <v>6020</v>
+        <v>6569</v>
       </c>
       <c r="D2" t="n">
-        <v>17629</v>
+        <v>20196</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2826</v>
+        <v>2412</v>
       </c>
       <c r="C3" t="n">
-        <v>2535</v>
+        <v>3921</v>
       </c>
       <c r="D3" t="n">
-        <v>15271</v>
+        <v>19133</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3129</v>
+        <v>2783</v>
       </c>
       <c r="C4" t="n">
-        <v>4731</v>
+        <v>6232</v>
       </c>
       <c r="D4" t="n">
-        <v>12713</v>
+        <v>15563</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2161</v>
+        <v>1792</v>
       </c>
       <c r="C5" t="n">
         <v>6475</v>
       </c>
       <c r="D5" t="n">
-        <v>6209</v>
+        <v>7616</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1121</v>
+        <v>904</v>
       </c>
       <c r="C6" t="n">
-        <v>6067</v>
+        <v>4865</v>
       </c>
       <c r="D6" t="n">
-        <v>1930</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>3624</v>
+        <v>3022</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1623</v>
+        <v>1539</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
         <v>299</v>
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2093</v>
+        <v>1792</v>
       </c>
       <c r="C2" t="n">
-        <v>2948</v>
+        <v>3231</v>
       </c>
       <c r="D2" t="n">
-        <v>12923</v>
+        <v>14427</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2502</v>
+        <v>2163</v>
       </c>
       <c r="C3" t="n">
-        <v>3602</v>
+        <v>4510</v>
       </c>
       <c r="D3" t="n">
-        <v>14723</v>
+        <v>18219</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2799</v>
+        <v>2462</v>
       </c>
       <c r="C4" t="n">
-        <v>3862</v>
+        <v>5327</v>
       </c>
       <c r="D4" t="n">
-        <v>12792</v>
+        <v>15719</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2330</v>
+        <v>1985</v>
       </c>
       <c r="C5" t="n">
-        <v>5890</v>
+        <v>6500</v>
       </c>
       <c r="D5" t="n">
-        <v>6888</v>
+        <v>8446</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1327</v>
+        <v>1062</v>
       </c>
       <c r="C6" t="n">
-        <v>6451</v>
+        <v>5564</v>
       </c>
       <c r="D6" t="n">
-        <v>2314</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="C7" t="n">
-        <v>4493</v>
+        <v>3679</v>
       </c>
       <c r="D7" t="n">
-        <v>810</v>
+        <v>891</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2118</v>
+        <v>1927</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -3366,10 +3366,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>613</v>
+        <v>626</v>
       </c>
       <c r="D9" t="n">
         <v>297</v>
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4311</v>
+        <v>2948</v>
       </c>
       <c r="C2" t="n">
-        <v>8625</v>
+        <v>4401</v>
       </c>
       <c r="D2" t="n">
-        <v>26108</v>
+        <v>24708</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1979</v>
+        <v>1709</v>
       </c>
       <c r="C3" t="n">
-        <v>2986</v>
+        <v>3544</v>
       </c>
       <c r="D3" t="n">
-        <v>13564</v>
+        <v>16597</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2362</v>
+        <v>2047</v>
       </c>
       <c r="C4" t="n">
-        <v>3669</v>
+        <v>4863</v>
       </c>
       <c r="D4" t="n">
-        <v>12558</v>
+        <v>15601</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2274</v>
+        <v>1960</v>
       </c>
       <c r="C5" t="n">
-        <v>4930</v>
+        <v>5880</v>
       </c>
       <c r="D5" t="n">
-        <v>7528</v>
+        <v>9085</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1559</v>
+        <v>1283</v>
       </c>
       <c r="C6" t="n">
-        <v>6174</v>
+        <v>5884</v>
       </c>
       <c r="D6" t="n">
-        <v>2898</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>460</v>
       </c>
       <c r="C7" t="n">
-        <v>5239</v>
+        <v>4434</v>
       </c>
       <c r="D7" t="n">
-        <v>993</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>2999</v>
+        <v>2544</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1120</v>
+        <v>1065</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6770</v>
+        <v>4406</v>
       </c>
       <c r="C2" t="n">
-        <v>3913</v>
+        <v>6527</v>
       </c>
       <c r="D2" t="n">
-        <v>21231</v>
+        <v>22134</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3048</v>
+        <v>2107</v>
       </c>
       <c r="C2" t="n">
-        <v>4830</v>
+        <v>2499</v>
       </c>
       <c r="D2" t="n">
-        <v>19216</v>
+        <v>18186</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2844</v>
+        <v>2360</v>
       </c>
       <c r="C3" t="n">
-        <v>4592</v>
+        <v>4049</v>
       </c>
       <c r="D3" t="n">
-        <v>15536</v>
+        <v>18562</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3284</v>
+        <v>2855</v>
       </c>
       <c r="C4" t="n">
-        <v>5333</v>
+        <v>6849</v>
       </c>
       <c r="D4" t="n">
-        <v>12946</v>
+        <v>16021</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1524</v>
+        <v>1239</v>
       </c>
       <c r="C5" t="n">
-        <v>8045</v>
+        <v>8393</v>
       </c>
       <c r="D5" t="n">
-        <v>6912</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>532</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>6404</v>
+        <v>5556</v>
       </c>
       <c r="D6" t="n">
-        <v>2266</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>2939</v>
+        <v>2493</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>1043</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6583</v>
+        <v>6942</v>
       </c>
       <c r="C2" t="n">
-        <v>5673</v>
+        <v>4733</v>
       </c>
       <c r="D2" t="n">
-        <v>20535</v>
+        <v>32183</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2876</v>
+        <v>1873</v>
       </c>
       <c r="C3" t="n">
-        <v>1972</v>
+        <v>3289</v>
       </c>
       <c r="D3" t="n">
-        <v>4206</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="4">
@@ -4616,7 +4616,7 @@
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5153</v>
+        <v>4338</v>
       </c>
       <c r="C2" t="n">
-        <v>7393</v>
+        <v>7453</v>
       </c>
       <c r="D2" t="n">
-        <v>24549</v>
+        <v>27860</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3886</v>
+        <v>3614</v>
       </c>
       <c r="C3" t="n">
-        <v>3506</v>
+        <v>3541</v>
       </c>
       <c r="D3" t="n">
-        <v>6639</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1284</v>
+        <v>848</v>
       </c>
       <c r="C4" t="n">
-        <v>1200</v>
+        <v>1972</v>
       </c>
       <c r="D4" t="n">
-        <v>2029</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4727</v>
+        <v>3814</v>
       </c>
       <c r="C2" t="n">
-        <v>9204</v>
+        <v>4404</v>
       </c>
       <c r="D2" t="n">
-        <v>26814</v>
+        <v>34113</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>3270</v>
       </c>
       <c r="C3" t="n">
-        <v>4869</v>
+        <v>4885</v>
       </c>
       <c r="D3" t="n">
-        <v>9026</v>
+        <v>11147</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2202</v>
+        <v>1891</v>
       </c>
       <c r="C4" t="n">
-        <v>2481</v>
+        <v>2785</v>
       </c>
       <c r="D4" t="n">
-        <v>2852</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>576</v>
+        <v>401</v>
       </c>
       <c r="C5" t="n">
-        <v>752</v>
+        <v>1176</v>
       </c>
       <c r="D5" t="n">
-        <v>1301</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5541</v>
+        <v>4078</v>
       </c>
       <c r="C2" t="n">
-        <v>4888</v>
+        <v>5012</v>
       </c>
       <c r="D2" t="n">
-        <v>22795</v>
+        <v>37063</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3451</v>
+        <v>2908</v>
       </c>
       <c r="C3" t="n">
-        <v>6180</v>
+        <v>4083</v>
       </c>
       <c r="D3" t="n">
-        <v>11094</v>
+        <v>13853</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2516</v>
+        <v>2167</v>
       </c>
       <c r="C4" t="n">
-        <v>3713</v>
+        <v>3809</v>
       </c>
       <c r="D4" t="n">
-        <v>3891</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1142</v>
+        <v>936</v>
       </c>
       <c r="C5" t="n">
-        <v>1625</v>
+        <v>1985</v>
       </c>
       <c r="D5" t="n">
-        <v>1516</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>529</v>
+        <v>734</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6614</v>
+        <v>4667</v>
       </c>
       <c r="C2" t="n">
-        <v>9584</v>
+        <v>4632</v>
       </c>
       <c r="D2" t="n">
-        <v>21504</v>
+        <v>32121</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3244</v>
+        <v>2530</v>
       </c>
       <c r="C3" t="n">
-        <v>4521</v>
+        <v>3728</v>
       </c>
       <c r="D3" t="n">
-        <v>11376</v>
+        <v>15434</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1841</v>
+        <v>1578</v>
       </c>
       <c r="C4" t="n">
-        <v>4155</v>
+        <v>3208</v>
       </c>
       <c r="D4" t="n">
-        <v>4437</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="C5" t="n">
-        <v>1969</v>
+        <v>2141</v>
       </c>
       <c r="D5" t="n">
-        <v>1511</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>341</v>
+        <v>274</v>
       </c>
       <c r="C6" t="n">
-        <v>728</v>
+        <v>906</v>
       </c>
       <c r="D6" t="n">
-        <v>804</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>279</v>
+        <v>345</v>
       </c>
       <c r="D7" t="n">
         <v>515</v>
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,7 +5868,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5535</v>
+        <v>4031</v>
       </c>
       <c r="C2" t="n">
-        <v>5618</v>
+        <v>4065</v>
       </c>
       <c r="D2" t="n">
-        <v>31114</v>
+        <v>32650</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4103</v>
+        <v>2976</v>
       </c>
       <c r="C3" t="n">
-        <v>6436</v>
+        <v>3658</v>
       </c>
       <c r="D3" t="n">
-        <v>12240</v>
+        <v>17101</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2233</v>
+        <v>1779</v>
       </c>
       <c r="C4" t="n">
-        <v>4289</v>
+        <v>3455</v>
       </c>
       <c r="D4" t="n">
-        <v>5658</v>
+        <v>7184</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>1062</v>
       </c>
       <c r="C5" t="n">
-        <v>3189</v>
+        <v>2721</v>
       </c>
       <c r="D5" t="n">
-        <v>2054</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>496</v>
       </c>
       <c r="C6" t="n">
-        <v>1433</v>
+        <v>1594</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>534</v>
+        <v>658</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5267</v>
+        <v>3705</v>
       </c>
       <c r="C2" t="n">
-        <v>6381</v>
+        <v>3406</v>
       </c>
       <c r="D2" t="n">
-        <v>32215</v>
+        <v>28786</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3952</v>
+        <v>2873</v>
       </c>
       <c r="C3" t="n">
-        <v>5184</v>
+        <v>3358</v>
       </c>
       <c r="D3" t="n">
-        <v>14378</v>
+        <v>18357</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2721</v>
+        <v>2045</v>
       </c>
       <c r="C4" t="n">
-        <v>5415</v>
+        <v>3498</v>
       </c>
       <c r="D4" t="n">
-        <v>6749</v>
+        <v>8869</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1518</v>
+        <v>1242</v>
       </c>
       <c r="C5" t="n">
-        <v>3724</v>
+        <v>3066</v>
       </c>
       <c r="D5" t="n">
-        <v>2629</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>841</v>
+        <v>708</v>
       </c>
       <c r="C6" t="n">
-        <v>2329</v>
+        <v>2170</v>
       </c>
       <c r="D6" t="n">
-        <v>1120</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>1009</v>
+        <v>1137</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>396</v>
+        <v>475</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_64_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4091</v>
+        <v>4876</v>
       </c>
       <c r="C2" t="n">
-        <v>6359</v>
+        <v>5964</v>
       </c>
       <c r="D2" t="n">
-        <v>26941</v>
+        <v>27899</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2709</v>
+        <v>3497</v>
       </c>
       <c r="C3" t="n">
-        <v>2949</v>
+        <v>5617</v>
       </c>
       <c r="D3" t="n">
-        <v>18649</v>
+        <v>15401</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2077</v>
+        <v>2744</v>
       </c>
       <c r="C4" t="n">
-        <v>3351</v>
+        <v>5921</v>
       </c>
       <c r="D4" t="n">
-        <v>10329</v>
+        <v>6874</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1420</v>
+        <v>1749</v>
       </c>
       <c r="C5" t="n">
-        <v>3222</v>
+        <v>4519</v>
       </c>
       <c r="D5" t="n">
-        <v>4036</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>988</v>
       </c>
       <c r="C6" t="n">
-        <v>2564</v>
+        <v>2497</v>
       </c>
       <c r="D6" t="n">
-        <v>1493</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="C7" t="n">
-        <v>1642</v>
+        <v>1338</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>786</v>
+        <v>627</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5908</v>
+        <v>5502</v>
       </c>
       <c r="C2" t="n">
-        <v>7791</v>
+        <v>8826</v>
       </c>
       <c r="D2" t="n">
-        <v>36447</v>
+        <v>41377</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2713</v>
+        <v>3375</v>
       </c>
       <c r="C3" t="n">
-        <v>3981</v>
+        <v>5075</v>
       </c>
       <c r="D3" t="n">
-        <v>18523</v>
+        <v>16065</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2013</v>
+        <v>2660</v>
       </c>
       <c r="C4" t="n">
-        <v>3084</v>
+        <v>5592</v>
       </c>
       <c r="D4" t="n">
-        <v>11273</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1512</v>
+        <v>1928</v>
       </c>
       <c r="C5" t="n">
-        <v>3184</v>
+        <v>5097</v>
       </c>
       <c r="D5" t="n">
-        <v>4940</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1028</v>
+        <v>1203</v>
       </c>
       <c r="C6" t="n">
-        <v>2841</v>
+        <v>3379</v>
       </c>
       <c r="D6" t="n">
-        <v>1848</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>556</v>
+        <v>625</v>
       </c>
       <c r="C7" t="n">
-        <v>2040</v>
+        <v>1871</v>
       </c>
       <c r="D7" t="n">
-        <v>829</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C8" t="n">
-        <v>1163</v>
+        <v>934</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
         <v>207</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8244</v>
+        <v>7402</v>
       </c>
       <c r="C2" t="n">
-        <v>14339</v>
+        <v>10308</v>
       </c>
       <c r="D2" t="n">
-        <v>40575</v>
+        <v>42071</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3253</v>
+        <v>3470</v>
       </c>
       <c r="C3" t="n">
-        <v>4954</v>
+        <v>5900</v>
       </c>
       <c r="D3" t="n">
-        <v>19602</v>
+        <v>18251</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1964</v>
+        <v>2526</v>
       </c>
       <c r="C4" t="n">
-        <v>3424</v>
+        <v>5242</v>
       </c>
       <c r="D4" t="n">
-        <v>12043</v>
+        <v>8987</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1545</v>
+        <v>1983</v>
       </c>
       <c r="C5" t="n">
-        <v>3044</v>
+        <v>5155</v>
       </c>
       <c r="D5" t="n">
-        <v>5654</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1120</v>
+        <v>1381</v>
       </c>
       <c r="C6" t="n">
-        <v>2959</v>
+        <v>4040</v>
       </c>
       <c r="D6" t="n">
-        <v>2268</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>671</v>
+        <v>770</v>
       </c>
       <c r="C7" t="n">
-        <v>2348</v>
+        <v>2505</v>
       </c>
       <c r="D7" t="n">
-        <v>952</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="C8" t="n">
-        <v>1503</v>
+        <v>1300</v>
       </c>
       <c r="D8" t="n">
-        <v>509</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>776</v>
+        <v>634</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7267</v>
+        <v>6669</v>
       </c>
       <c r="C2" t="n">
-        <v>9635</v>
+        <v>6926</v>
       </c>
       <c r="D2" t="n">
-        <v>33212</v>
+        <v>34357</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3779</v>
+        <v>4369</v>
       </c>
       <c r="C3" t="n">
-        <v>7938</v>
+        <v>9046</v>
       </c>
       <c r="D3" t="n">
-        <v>21649</v>
+        <v>19494</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1427</v>
+        <v>1832</v>
       </c>
       <c r="C4" t="n">
-        <v>4861</v>
+        <v>7917</v>
       </c>
       <c r="D4" t="n">
-        <v>11831</v>
+        <v>8418</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1034</v>
+        <v>1276</v>
       </c>
       <c r="C5" t="n">
-        <v>2899</v>
+        <v>3959</v>
       </c>
       <c r="D5" t="n">
-        <v>3796</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>620</v>
+        <v>711</v>
       </c>
       <c r="C6" t="n">
-        <v>2301</v>
+        <v>2454</v>
       </c>
       <c r="D6" t="n">
-        <v>932</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="C7" t="n">
-        <v>1472</v>
+        <v>1274</v>
       </c>
       <c r="D7" t="n">
-        <v>498</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>760</v>
+        <v>621</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4140</v>
+        <v>4026</v>
       </c>
       <c r="C2" t="n">
-        <v>3993</v>
+        <v>3006</v>
       </c>
       <c r="D2" t="n">
-        <v>23347</v>
+        <v>24446</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4476</v>
+        <v>4606</v>
       </c>
       <c r="C3" t="n">
-        <v>7894</v>
+        <v>7310</v>
       </c>
       <c r="D3" t="n">
-        <v>21974</v>
+        <v>20392</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2038</v>
+        <v>2457</v>
       </c>
       <c r="C4" t="n">
-        <v>6393</v>
+        <v>8511</v>
       </c>
       <c r="D4" t="n">
-        <v>13206</v>
+        <v>10024</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1125</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="n">
-        <v>3759</v>
+        <v>5738</v>
       </c>
       <c r="D5" t="n">
-        <v>4756</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>855</v>
       </c>
       <c r="C6" t="n">
-        <v>2653</v>
+        <v>3137</v>
       </c>
       <c r="D6" t="n">
-        <v>1222</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>1828</v>
+        <v>1697</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>984</v>
+        <v>830</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3285</v>
+        <v>4667</v>
       </c>
       <c r="C2" t="n">
-        <v>6600</v>
+        <v>5731</v>
       </c>
       <c r="D2" t="n">
-        <v>25991</v>
+        <v>19831</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3636</v>
+        <v>3661</v>
       </c>
       <c r="C3" t="n">
-        <v>5330</v>
+        <v>4642</v>
       </c>
       <c r="D3" t="n">
-        <v>20870</v>
+        <v>19768</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2660</v>
+        <v>2925</v>
       </c>
       <c r="C4" t="n">
-        <v>7009</v>
+        <v>7734</v>
       </c>
       <c r="D4" t="n">
-        <v>14108</v>
+        <v>11315</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1342</v>
+        <v>1655</v>
       </c>
       <c r="C5" t="n">
-        <v>4981</v>
+        <v>7004</v>
       </c>
       <c r="D5" t="n">
-        <v>5990</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>829</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>3126</v>
+        <v>4279</v>
       </c>
       <c r="D6" t="n">
-        <v>1748</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="C7" t="n">
-        <v>2209</v>
+        <v>2347</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1340</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>631</v>
+        <v>541</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1927</v>
+        <v>2726</v>
       </c>
       <c r="C2" t="n">
-        <v>3028</v>
+        <v>2648</v>
       </c>
       <c r="D2" t="n">
-        <v>17994</v>
+        <v>13673</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3452</v>
+        <v>3802</v>
       </c>
       <c r="C3" t="n">
-        <v>5596</v>
+        <v>4868</v>
       </c>
       <c r="D3" t="n">
-        <v>20942</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2948</v>
+        <v>3234</v>
       </c>
       <c r="C4" t="n">
-        <v>6971</v>
+        <v>7276</v>
       </c>
       <c r="D4" t="n">
-        <v>15062</v>
+        <v>12365</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1413</v>
+        <v>1732</v>
       </c>
       <c r="C5" t="n">
-        <v>6195</v>
+        <v>8237</v>
       </c>
       <c r="D5" t="n">
-        <v>6423</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>844</v>
       </c>
       <c r="C6" t="n">
-        <v>3889</v>
+        <v>5123</v>
       </c>
       <c r="D6" t="n">
-        <v>1677</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2365</v>
+        <v>2359</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1038</v>
+        <v>904</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2587</v>
+        <v>2843</v>
       </c>
       <c r="C2" t="n">
-        <v>6569</v>
+        <v>8543</v>
       </c>
       <c r="D2" t="n">
-        <v>20196</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2412</v>
+        <v>2859</v>
       </c>
       <c r="C3" t="n">
-        <v>3921</v>
+        <v>3417</v>
       </c>
       <c r="D3" t="n">
-        <v>19133</v>
+        <v>17237</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2783</v>
+        <v>3059</v>
       </c>
       <c r="C4" t="n">
-        <v>6232</v>
+        <v>6038</v>
       </c>
       <c r="D4" t="n">
-        <v>15563</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>2080</v>
       </c>
       <c r="C5" t="n">
-        <v>6475</v>
+        <v>7711</v>
       </c>
       <c r="D5" t="n">
-        <v>7616</v>
+        <v>5649</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>4865</v>
+        <v>6441</v>
       </c>
       <c r="D6" t="n">
-        <v>2293</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>3022</v>
+        <v>3514</v>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1539</v>
+        <v>1448</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>481</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1792</v>
+        <v>2149</v>
       </c>
       <c r="C2" t="n">
-        <v>3231</v>
+        <v>4195</v>
       </c>
       <c r="D2" t="n">
-        <v>14427</v>
+        <v>10996</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2163</v>
+        <v>2499</v>
       </c>
       <c r="C3" t="n">
-        <v>4510</v>
+        <v>4945</v>
       </c>
       <c r="D3" t="n">
-        <v>18219</v>
+        <v>15833</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2462</v>
+        <v>2761</v>
       </c>
       <c r="C4" t="n">
-        <v>5327</v>
+        <v>5004</v>
       </c>
       <c r="D4" t="n">
-        <v>15719</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1985</v>
+        <v>2271</v>
       </c>
       <c r="C5" t="n">
-        <v>6500</v>
+        <v>7236</v>
       </c>
       <c r="D5" t="n">
-        <v>8446</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1062</v>
+        <v>1261</v>
       </c>
       <c r="C6" t="n">
-        <v>5564</v>
+        <v>7102</v>
       </c>
       <c r="D6" t="n">
-        <v>2770</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>3679</v>
+        <v>4470</v>
       </c>
       <c r="D7" t="n">
-        <v>891</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1927</v>
+        <v>1917</v>
       </c>
       <c r="D8" t="n">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>626</v>
+        <v>567</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2948</v>
+        <v>4422</v>
       </c>
       <c r="C2" t="n">
-        <v>4401</v>
+        <v>7646</v>
       </c>
       <c r="D2" t="n">
-        <v>24708</v>
+        <v>19683</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1709</v>
+        <v>1998</v>
       </c>
       <c r="C3" t="n">
-        <v>3544</v>
+        <v>4168</v>
       </c>
       <c r="D3" t="n">
-        <v>16597</v>
+        <v>14239</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2047</v>
+        <v>2319</v>
       </c>
       <c r="C4" t="n">
-        <v>4863</v>
+        <v>4826</v>
       </c>
       <c r="D4" t="n">
-        <v>15601</v>
+        <v>13342</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1960</v>
+        <v>2247</v>
       </c>
       <c r="C5" t="n">
-        <v>5880</v>
+        <v>6164</v>
       </c>
       <c r="D5" t="n">
-        <v>9085</v>
+        <v>7184</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1283</v>
+        <v>1477</v>
       </c>
       <c r="C6" t="n">
-        <v>5884</v>
+        <v>7163</v>
       </c>
       <c r="D6" t="n">
-        <v>3496</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="C7" t="n">
-        <v>4434</v>
+        <v>5448</v>
       </c>
       <c r="D7" t="n">
-        <v>1121</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>2544</v>
+        <v>2816</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1065</v>
+        <v>1022</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4406</v>
+        <v>4394</v>
       </c>
       <c r="C2" t="n">
-        <v>6527</v>
+        <v>3503</v>
       </c>
       <c r="D2" t="n">
-        <v>22134</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2107</v>
+        <v>3160</v>
       </c>
       <c r="C2" t="n">
-        <v>2499</v>
+        <v>4342</v>
       </c>
       <c r="D2" t="n">
-        <v>18186</v>
+        <v>14486</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2360</v>
+        <v>2822</v>
       </c>
       <c r="C3" t="n">
-        <v>4049</v>
+        <v>5335</v>
       </c>
       <c r="D3" t="n">
-        <v>18562</v>
+        <v>15825</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2855</v>
+        <v>3258</v>
       </c>
       <c r="C4" t="n">
-        <v>6849</v>
+        <v>6966</v>
       </c>
       <c r="D4" t="n">
-        <v>16021</v>
+        <v>13635</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1239</v>
+        <v>1427</v>
       </c>
       <c r="C5" t="n">
-        <v>8393</v>
+        <v>9639</v>
       </c>
       <c r="D5" t="n">
-        <v>8341</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>425</v>
+        <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>5556</v>
+        <v>6742</v>
       </c>
       <c r="D6" t="n">
-        <v>2668</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>2493</v>
+        <v>2759</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1043</v>
+        <v>1001</v>
       </c>
       <c r="D8" t="n">
         <v>303</v>
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6942</v>
+        <v>6524</v>
       </c>
       <c r="C2" t="n">
-        <v>4733</v>
+        <v>5006</v>
       </c>
       <c r="D2" t="n">
-        <v>32183</v>
+        <v>8322</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1873</v>
+        <v>1868</v>
       </c>
       <c r="C3" t="n">
-        <v>3289</v>
+        <v>1793</v>
       </c>
       <c r="D3" t="n">
-        <v>4357</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4">
@@ -4543,10 +4543,10 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="5">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4338</v>
+        <v>4849</v>
       </c>
       <c r="C2" t="n">
-        <v>7453</v>
+        <v>4700</v>
       </c>
       <c r="D2" t="n">
-        <v>27860</v>
+        <v>17803</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3614</v>
+        <v>3477</v>
       </c>
       <c r="C3" t="n">
-        <v>3541</v>
+        <v>3137</v>
       </c>
       <c r="D3" t="n">
-        <v>8711</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>848</v>
+        <v>861</v>
       </c>
       <c r="C4" t="n">
-        <v>1972</v>
+        <v>1110</v>
       </c>
       <c r="D4" t="n">
-        <v>2059</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3814</v>
+        <v>4441</v>
       </c>
       <c r="C2" t="n">
-        <v>4404</v>
+        <v>5005</v>
       </c>
       <c r="D2" t="n">
-        <v>34113</v>
+        <v>22884</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3270</v>
+        <v>3420</v>
       </c>
       <c r="C3" t="n">
-        <v>4885</v>
+        <v>3460</v>
       </c>
       <c r="D3" t="n">
-        <v>11147</v>
+        <v>4832</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1891</v>
+        <v>1862</v>
       </c>
       <c r="C4" t="n">
-        <v>2785</v>
+        <v>2254</v>
       </c>
       <c r="D4" t="n">
-        <v>3273</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C5" t="n">
-        <v>1176</v>
+        <v>710</v>
       </c>
       <c r="D5" t="n">
-        <v>1307</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4078</v>
+        <v>5274</v>
       </c>
       <c r="C2" t="n">
-        <v>5012</v>
+        <v>8221</v>
       </c>
       <c r="D2" t="n">
-        <v>37063</v>
+        <v>24950</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2908</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>4083</v>
+        <v>3710</v>
       </c>
       <c r="D3" t="n">
-        <v>13853</v>
+        <v>7235</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2167</v>
+        <v>2255</v>
       </c>
       <c r="C4" t="n">
-        <v>3809</v>
+        <v>2867</v>
       </c>
       <c r="D4" t="n">
-        <v>4609</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C5" t="n">
-        <v>1985</v>
+        <v>1503</v>
       </c>
       <c r="D5" t="n">
-        <v>1594</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C6" t="n">
-        <v>734</v>
+        <v>510</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
         <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>285</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4667</v>
+        <v>6481</v>
       </c>
       <c r="C2" t="n">
-        <v>4632</v>
+        <v>10944</v>
       </c>
       <c r="D2" t="n">
-        <v>32121</v>
+        <v>34425</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2530</v>
+        <v>3082</v>
       </c>
       <c r="C3" t="n">
-        <v>3728</v>
+        <v>4960</v>
       </c>
       <c r="D3" t="n">
-        <v>15434</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1578</v>
+        <v>1698</v>
       </c>
       <c r="C4" t="n">
-        <v>3208</v>
+        <v>2717</v>
       </c>
       <c r="D4" t="n">
-        <v>5370</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="C5" t="n">
-        <v>2141</v>
+        <v>1637</v>
       </c>
       <c r="D5" t="n">
-        <v>1661</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C6" t="n">
-        <v>906</v>
+        <v>684</v>
       </c>
       <c r="D6" t="n">
-        <v>815</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>271</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5983,10 +5983,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4031</v>
+        <v>5093</v>
       </c>
       <c r="C2" t="n">
-        <v>4065</v>
+        <v>6986</v>
       </c>
       <c r="D2" t="n">
-        <v>32650</v>
+        <v>27609</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2976</v>
+        <v>4007</v>
       </c>
       <c r="C3" t="n">
-        <v>3658</v>
+        <v>7357</v>
       </c>
       <c r="D3" t="n">
-        <v>17101</v>
+        <v>12693</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1779</v>
+        <v>2112</v>
       </c>
       <c r="C4" t="n">
-        <v>3455</v>
+        <v>4060</v>
       </c>
       <c r="D4" t="n">
-        <v>7184</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1062</v>
+        <v>1133</v>
       </c>
       <c r="C5" t="n">
-        <v>2721</v>
+        <v>2256</v>
       </c>
       <c r="D5" t="n">
-        <v>2358</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>496</v>
+        <v>529</v>
       </c>
       <c r="C6" t="n">
-        <v>1594</v>
+        <v>1233</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>658</v>
+        <v>512</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3705</v>
+        <v>4758</v>
       </c>
       <c r="C2" t="n">
-        <v>3406</v>
+        <v>6728</v>
       </c>
       <c r="D2" t="n">
-        <v>28786</v>
+        <v>27733</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2873</v>
+        <v>3784</v>
       </c>
       <c r="C3" t="n">
-        <v>3358</v>
+        <v>6163</v>
       </c>
       <c r="D3" t="n">
-        <v>18357</v>
+        <v>14386</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2045</v>
+        <v>2624</v>
       </c>
       <c r="C4" t="n">
-        <v>3498</v>
+        <v>5906</v>
       </c>
       <c r="D4" t="n">
-        <v>8869</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>1436</v>
       </c>
       <c r="C5" t="n">
-        <v>3066</v>
+        <v>3230</v>
       </c>
       <c r="D5" t="n">
-        <v>3143</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>708</v>
+        <v>755</v>
       </c>
       <c r="C6" t="n">
-        <v>2170</v>
+        <v>1778</v>
       </c>
       <c r="D6" t="n">
-        <v>1205</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>1137</v>
+        <v>900</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>475</v>
+        <v>384</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_64_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4876</v>
+        <v>1361</v>
       </c>
       <c r="C2" t="n">
-        <v>5964</v>
+        <v>4742</v>
       </c>
       <c r="D2" t="n">
-        <v>27899</v>
+        <v>11820</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3497</v>
+        <v>2331</v>
       </c>
       <c r="C3" t="n">
-        <v>5617</v>
+        <v>10854</v>
       </c>
       <c r="D3" t="n">
-        <v>15401</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2744</v>
+        <v>1683</v>
       </c>
       <c r="C4" t="n">
-        <v>5921</v>
+        <v>11028</v>
       </c>
       <c r="D4" t="n">
-        <v>6874</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1749</v>
+        <v>903</v>
       </c>
       <c r="C5" t="n">
-        <v>4519</v>
+        <v>6541</v>
       </c>
       <c r="D5" t="n">
-        <v>2358</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>2497</v>
+        <v>2611</v>
       </c>
       <c r="D6" t="n">
-        <v>1041</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>1338</v>
+        <v>855</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>627</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5502</v>
+        <v>1069</v>
       </c>
       <c r="C2" t="n">
-        <v>8826</v>
+        <v>8493</v>
       </c>
       <c r="D2" t="n">
-        <v>41377</v>
+        <v>17831</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3375</v>
+        <v>1593</v>
       </c>
       <c r="C3" t="n">
-        <v>5075</v>
+        <v>6775</v>
       </c>
       <c r="D3" t="n">
-        <v>16065</v>
+        <v>10572</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2660</v>
+        <v>1725</v>
       </c>
       <c r="C4" t="n">
+        <v>10812</v>
+      </c>
+      <c r="D4" t="n">
         <v>5592</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7990</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1928</v>
+        <v>1119</v>
       </c>
       <c r="C5" t="n">
-        <v>5097</v>
+        <v>8644</v>
       </c>
       <c r="D5" t="n">
-        <v>3023</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1203</v>
+        <v>539</v>
       </c>
       <c r="C6" t="n">
-        <v>3379</v>
+        <v>4495</v>
       </c>
       <c r="D6" t="n">
-        <v>1219</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>1871</v>
+        <v>1671</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>934</v>
+        <v>575</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7402</v>
+        <v>590</v>
       </c>
       <c r="C2" t="n">
-        <v>10308</v>
+        <v>3715</v>
       </c>
       <c r="D2" t="n">
-        <v>42071</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3470</v>
+        <v>1400</v>
       </c>
       <c r="C3" t="n">
-        <v>5900</v>
+        <v>7157</v>
       </c>
       <c r="D3" t="n">
-        <v>18251</v>
+        <v>11172</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2526</v>
+        <v>1886</v>
       </c>
       <c r="C4" t="n">
-        <v>5242</v>
+        <v>10256</v>
       </c>
       <c r="D4" t="n">
-        <v>8987</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1983</v>
+        <v>1116</v>
       </c>
       <c r="C5" t="n">
-        <v>5155</v>
+        <v>10278</v>
       </c>
       <c r="D5" t="n">
-        <v>3617</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>404</v>
       </c>
       <c r="C6" t="n">
-        <v>4040</v>
+        <v>5511</v>
       </c>
       <c r="D6" t="n">
-        <v>1462</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>770</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2505</v>
+        <v>1518</v>
       </c>
       <c r="D7" t="n">
-        <v>752</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>358</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1300</v>
+        <v>501</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>634</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6669</v>
+        <v>809</v>
       </c>
       <c r="C2" t="n">
-        <v>6926</v>
+        <v>4592</v>
       </c>
       <c r="D2" t="n">
-        <v>34357</v>
+        <v>17285</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4369</v>
+        <v>906</v>
       </c>
       <c r="C3" t="n">
-        <v>9046</v>
+        <v>4873</v>
       </c>
       <c r="D3" t="n">
-        <v>19494</v>
+        <v>10656</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1832</v>
+        <v>1485</v>
       </c>
       <c r="C4" t="n">
-        <v>7917</v>
+        <v>8594</v>
       </c>
       <c r="D4" t="n">
-        <v>8418</v>
+        <v>6878</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1291</v>
       </c>
       <c r="C5" t="n">
-        <v>3959</v>
+        <v>10152</v>
       </c>
       <c r="D5" t="n">
-        <v>2439</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>711</v>
+        <v>615</v>
       </c>
       <c r="C6" t="n">
-        <v>2454</v>
+        <v>7617</v>
       </c>
       <c r="D6" t="n">
-        <v>736</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>1274</v>
+        <v>3229</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>621</v>
+        <v>904</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4026</v>
+        <v>473</v>
       </c>
       <c r="C2" t="n">
-        <v>3006</v>
+        <v>2941</v>
       </c>
       <c r="D2" t="n">
-        <v>24446</v>
+        <v>12591</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4606</v>
+        <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>7310</v>
+        <v>4299</v>
       </c>
       <c r="D3" t="n">
-        <v>20392</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2457</v>
+        <v>1208</v>
       </c>
       <c r="C4" t="n">
-        <v>8511</v>
+        <v>7055</v>
       </c>
       <c r="D4" t="n">
-        <v>10024</v>
+        <v>7242</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1317</v>
       </c>
       <c r="C5" t="n">
-        <v>5738</v>
+        <v>9732</v>
       </c>
       <c r="D5" t="n">
-        <v>3157</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>855</v>
+        <v>746</v>
       </c>
       <c r="C6" t="n">
-        <v>3137</v>
+        <v>8762</v>
       </c>
       <c r="D6" t="n">
-        <v>912</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>1697</v>
+        <v>4610</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>830</v>
+        <v>1412</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4667</v>
+        <v>648</v>
       </c>
       <c r="C2" t="n">
-        <v>5731</v>
+        <v>8820</v>
       </c>
       <c r="D2" t="n">
-        <v>19831</v>
+        <v>17705</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3661</v>
+        <v>551</v>
       </c>
       <c r="C3" t="n">
-        <v>4642</v>
+        <v>3334</v>
       </c>
       <c r="D3" t="n">
-        <v>19768</v>
+        <v>10490</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2925</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>7734</v>
+        <v>5691</v>
       </c>
       <c r="D4" t="n">
-        <v>11315</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1655</v>
+        <v>1175</v>
       </c>
       <c r="C5" t="n">
-        <v>7004</v>
+        <v>8398</v>
       </c>
       <c r="D5" t="n">
-        <v>4181</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>884</v>
       </c>
       <c r="C6" t="n">
-        <v>4279</v>
+        <v>9075</v>
       </c>
       <c r="D6" t="n">
-        <v>1244</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>2347</v>
+        <v>6280</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1194</v>
+        <v>2571</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>541</v>
+        <v>756</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2726</v>
+        <v>456</v>
       </c>
       <c r="C2" t="n">
-        <v>2648</v>
+        <v>4940</v>
       </c>
       <c r="D2" t="n">
-        <v>13673</v>
+        <v>13030</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3802</v>
+        <v>812</v>
       </c>
       <c r="C3" t="n">
-        <v>4868</v>
+        <v>4933</v>
       </c>
       <c r="D3" t="n">
-        <v>19300</v>
+        <v>11641</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3234</v>
+        <v>1541</v>
       </c>
       <c r="C4" t="n">
-        <v>7276</v>
+        <v>8346</v>
       </c>
       <c r="D4" t="n">
-        <v>12365</v>
+        <v>7703</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1732</v>
+        <v>860</v>
       </c>
       <c r="C5" t="n">
-        <v>8237</v>
+        <v>12588</v>
       </c>
       <c r="D5" t="n">
-        <v>4542</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>844</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>5123</v>
+        <v>8022</v>
       </c>
       <c r="D6" t="n">
-        <v>1220</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>2359</v>
+        <v>2519</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>904</v>
+        <v>740</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2843</v>
+        <v>269</v>
       </c>
       <c r="C2" t="n">
-        <v>8543</v>
+        <v>3110</v>
       </c>
       <c r="D2" t="n">
-        <v>13355</v>
+        <v>9407</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2859</v>
+        <v>571</v>
       </c>
       <c r="C3" t="n">
-        <v>3417</v>
+        <v>4367</v>
       </c>
       <c r="D3" t="n">
-        <v>17237</v>
+        <v>11012</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3059</v>
+        <v>1025</v>
       </c>
       <c r="C4" t="n">
-        <v>6038</v>
+        <v>6341</v>
       </c>
       <c r="D4" t="n">
-        <v>13120</v>
+        <v>7762</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2080</v>
+        <v>801</v>
       </c>
       <c r="C5" t="n">
-        <v>7711</v>
+        <v>9392</v>
       </c>
       <c r="D5" t="n">
-        <v>5649</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>6441</v>
+        <v>8143</v>
       </c>
       <c r="D6" t="n">
-        <v>1650</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
-        <v>3514</v>
+        <v>3352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1448</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>481</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>117</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2149</v>
+        <v>241</v>
       </c>
       <c r="C2" t="n">
-        <v>4195</v>
+        <v>6845</v>
       </c>
       <c r="D2" t="n">
-        <v>10996</v>
+        <v>12015</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2499</v>
+        <v>366</v>
       </c>
       <c r="C3" t="n">
-        <v>4945</v>
+        <v>3279</v>
       </c>
       <c r="D3" t="n">
-        <v>15833</v>
+        <v>9992</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2761</v>
+        <v>716</v>
       </c>
       <c r="C4" t="n">
-        <v>5004</v>
+        <v>5166</v>
       </c>
       <c r="D4" t="n">
-        <v>13400</v>
+        <v>8118</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2271</v>
+        <v>819</v>
       </c>
       <c r="C5" t="n">
-        <v>7236</v>
+        <v>7644</v>
       </c>
       <c r="D5" t="n">
-        <v>6446</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1261</v>
+        <v>461</v>
       </c>
       <c r="C6" t="n">
-        <v>7102</v>
+        <v>8747</v>
       </c>
       <c r="D6" t="n">
-        <v>2008</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>4470</v>
+        <v>5604</v>
       </c>
       <c r="D7" t="n">
-        <v>748</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1917</v>
+        <v>1998</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4422</v>
+        <v>950</v>
       </c>
       <c r="C2" t="n">
-        <v>7646</v>
+        <v>12160</v>
       </c>
       <c r="D2" t="n">
-        <v>19683</v>
+        <v>13325</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1998</v>
+        <v>261</v>
       </c>
       <c r="C3" t="n">
-        <v>4168</v>
+        <v>4311</v>
       </c>
       <c r="D3" t="n">
-        <v>14239</v>
+        <v>9595</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2319</v>
+        <v>496</v>
       </c>
       <c r="C4" t="n">
-        <v>4826</v>
+        <v>4152</v>
       </c>
       <c r="D4" t="n">
-        <v>13342</v>
+        <v>8177</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2247</v>
+        <v>713</v>
       </c>
       <c r="C5" t="n">
-        <v>6164</v>
+        <v>6269</v>
       </c>
       <c r="D5" t="n">
-        <v>7184</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1477</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>7163</v>
+        <v>8163</v>
       </c>
       <c r="D6" t="n">
-        <v>2516</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>236</v>
       </c>
       <c r="C7" t="n">
-        <v>5448</v>
+        <v>6987</v>
       </c>
       <c r="D7" t="n">
-        <v>900</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2816</v>
+        <v>3516</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1022</v>
+        <v>1113</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4394</v>
+        <v>7727</v>
       </c>
       <c r="C2" t="n">
-        <v>3503</v>
+        <v>13297</v>
       </c>
       <c r="D2" t="n">
-        <v>5298</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3160</v>
+        <v>893</v>
       </c>
       <c r="C2" t="n">
-        <v>4342</v>
+        <v>24199</v>
       </c>
       <c r="D2" t="n">
-        <v>14486</v>
+        <v>12641</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2822</v>
+        <v>421</v>
       </c>
       <c r="C3" t="n">
-        <v>5335</v>
+        <v>6653</v>
       </c>
       <c r="D3" t="n">
-        <v>15825</v>
+        <v>9428</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3258</v>
+        <v>352</v>
       </c>
       <c r="C4" t="n">
-        <v>6966</v>
+        <v>4134</v>
       </c>
       <c r="D4" t="n">
-        <v>13635</v>
+        <v>8054</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1427</v>
+        <v>580</v>
       </c>
       <c r="C5" t="n">
-        <v>9639</v>
+        <v>5204</v>
       </c>
       <c r="D5" t="n">
-        <v>6405</v>
+        <v>4997</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>499</v>
+        <v>574</v>
       </c>
       <c r="C6" t="n">
-        <v>6742</v>
+        <v>7327</v>
       </c>
       <c r="D6" t="n">
-        <v>2000</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>2759</v>
+        <v>7376</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>1001</v>
+        <v>4841</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>1972</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>590</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>38</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6524</v>
+        <v>5250</v>
       </c>
       <c r="C2" t="n">
-        <v>5006</v>
+        <v>15228</v>
       </c>
       <c r="D2" t="n">
-        <v>8322</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1868</v>
+        <v>2549</v>
       </c>
       <c r="C3" t="n">
-        <v>1793</v>
+        <v>5251</v>
       </c>
       <c r="D3" t="n">
-        <v>1563</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4849</v>
+        <v>3919</v>
       </c>
       <c r="C2" t="n">
-        <v>4700</v>
+        <v>6361</v>
       </c>
       <c r="D2" t="n">
-        <v>17803</v>
+        <v>14411</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3477</v>
+        <v>3267</v>
       </c>
       <c r="C3" t="n">
-        <v>3137</v>
+        <v>9682</v>
       </c>
       <c r="D3" t="n">
-        <v>2583</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>861</v>
+        <v>1202</v>
       </c>
       <c r="C4" t="n">
-        <v>1110</v>
+        <v>3324</v>
       </c>
       <c r="D4" t="n">
-        <v>1502</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1188</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>308</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>348</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4441</v>
+        <v>2955</v>
       </c>
       <c r="C2" t="n">
-        <v>5005</v>
+        <v>7683</v>
       </c>
       <c r="D2" t="n">
-        <v>22884</v>
+        <v>24976</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3420</v>
+        <v>2994</v>
       </c>
       <c r="C3" t="n">
-        <v>3460</v>
+        <v>6687</v>
       </c>
       <c r="D3" t="n">
-        <v>4832</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1862</v>
+        <v>1931</v>
       </c>
       <c r="C4" t="n">
-        <v>2254</v>
+        <v>7039</v>
       </c>
       <c r="D4" t="n">
-        <v>1649</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>413</v>
+        <v>560</v>
       </c>
       <c r="C5" t="n">
-        <v>710</v>
+        <v>1997</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>282</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5274</v>
+        <v>2436</v>
       </c>
       <c r="C2" t="n">
-        <v>8221</v>
+        <v>10031</v>
       </c>
       <c r="D2" t="n">
-        <v>24950</v>
+        <v>23949</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>2459</v>
       </c>
       <c r="C3" t="n">
-        <v>3710</v>
+        <v>6261</v>
       </c>
       <c r="D3" t="n">
-        <v>7235</v>
+        <v>6989</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2255</v>
+        <v>2121</v>
       </c>
       <c r="C4" t="n">
-        <v>2867</v>
+        <v>6696</v>
       </c>
       <c r="D4" t="n">
-        <v>2163</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>939</v>
+        <v>1057</v>
       </c>
       <c r="C5" t="n">
-        <v>1503</v>
+        <v>4646</v>
       </c>
       <c r="D5" t="n">
-        <v>1254</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>510</v>
+        <v>1175</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>345</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6481</v>
+        <v>2629</v>
       </c>
       <c r="C2" t="n">
-        <v>10944</v>
+        <v>9242</v>
       </c>
       <c r="D2" t="n">
-        <v>34425</v>
+        <v>22486</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3082</v>
+        <v>2048</v>
       </c>
       <c r="C3" t="n">
-        <v>4960</v>
+        <v>7118</v>
       </c>
       <c r="D3" t="n">
-        <v>8860</v>
+        <v>9074</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1698</v>
+        <v>1954</v>
       </c>
       <c r="C4" t="n">
-        <v>2717</v>
+        <v>6327</v>
       </c>
       <c r="D4" t="n">
-        <v>2620</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>841</v>
+        <v>1361</v>
       </c>
       <c r="C5" t="n">
-        <v>1637</v>
+        <v>5592</v>
       </c>
       <c r="D5" t="n">
-        <v>1120</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>282</v>
+        <v>568</v>
       </c>
       <c r="C6" t="n">
-        <v>684</v>
+        <v>2861</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>277</v>
+        <v>715</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5093</v>
+        <v>2712</v>
       </c>
       <c r="C2" t="n">
-        <v>6986</v>
+        <v>18655</v>
       </c>
       <c r="D2" t="n">
-        <v>27609</v>
+        <v>20959</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4007</v>
+        <v>1895</v>
       </c>
       <c r="C3" t="n">
-        <v>7357</v>
+        <v>7119</v>
       </c>
       <c r="D3" t="n">
-        <v>12693</v>
+        <v>10288</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2112</v>
+        <v>1715</v>
       </c>
       <c r="C4" t="n">
-        <v>4060</v>
+        <v>6582</v>
       </c>
       <c r="D4" t="n">
-        <v>3858</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1133</v>
+        <v>1449</v>
       </c>
       <c r="C5" t="n">
-        <v>2256</v>
+        <v>5821</v>
       </c>
       <c r="D5" t="n">
-        <v>1377</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>529</v>
+        <v>815</v>
       </c>
       <c r="C6" t="n">
-        <v>1233</v>
+        <v>4037</v>
       </c>
       <c r="D6" t="n">
-        <v>813</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>512</v>
+        <v>1682</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>252</v>
+        <v>477</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4758</v>
+        <v>2508</v>
       </c>
       <c r="C2" t="n">
-        <v>6728</v>
+        <v>11939</v>
       </c>
       <c r="D2" t="n">
-        <v>27733</v>
+        <v>16728</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3784</v>
+        <v>2736</v>
       </c>
       <c r="C3" t="n">
-        <v>6163</v>
+        <v>12156</v>
       </c>
       <c r="D3" t="n">
-        <v>14386</v>
+        <v>10969</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2624</v>
+        <v>1338</v>
       </c>
       <c r="C4" t="n">
-        <v>5906</v>
+        <v>9568</v>
       </c>
       <c r="D4" t="n">
-        <v>5400</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1436</v>
+        <v>753</v>
       </c>
       <c r="C5" t="n">
-        <v>3230</v>
+        <v>3956</v>
       </c>
       <c r="D5" t="n">
-        <v>1811</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>755</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>1778</v>
+        <v>1648</v>
       </c>
       <c r="D6" t="n">
-        <v>896</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>900</v>
+        <v>467</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
